--- a/samples/sample_1/SAFE_VESSELS_INVENTORY_20251201.XLSX
+++ b/samples/sample_1/SAFE_VESSELS_INVENTORY_20251201.XLSX
@@ -1,130 +1,151 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Sheet2" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Sheet3" state="visible" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
-  <si>
-    <t>SHIPID</t>
-  </si>
-  <si>
-    <t>SHIPNAME</t>
-  </si>
-  <si>
-    <t>CUSTNO</t>
-  </si>
-  <si>
-    <t>ITEM</t>
-  </si>
-  <si>
-    <t>EDITION</t>
-  </si>
-  <si>
-    <t>STOREEDT</t>
-  </si>
-  <si>
-    <t>DESCRIP</t>
-  </si>
-  <si>
-    <t>ship 01</t>
-  </si>
-  <si>
-    <t>eagle</t>
-  </si>
-  <si>
-    <t>cust 001</t>
-  </si>
-  <si>
-    <t>item 1</t>
-  </si>
-  <si>
-    <t>2026</t>
-  </si>
-  <si>
-    <t>chart</t>
-  </si>
-  <si>
-    <t>item 2</t>
-  </si>
-  <si>
-    <t>2025 (3)</t>
-  </si>
-  <si>
-    <t>book</t>
-  </si>
-  <si>
-    <t>item 3</t>
-  </si>
-  <si>
-    <t>1.2.0</t>
-  </si>
-  <si>
-    <t>software</t>
-  </si>
-  <si>
-    <t>ship 02</t>
-  </si>
-  <si>
-    <t>hawk</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>ship 03</t>
-  </si>
-  <si>
-    <t>falcon</t>
-  </si>
-  <si>
-    <t>3</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="28">
+  <si>
+    <t xml:space="preserve">SHIPID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHIPNAME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUSTNO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDITION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STOREEDT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESCRIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ship 01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eagle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cust 001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 (3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ship 02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hawk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">compass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ship 03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">falcon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 (1)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <charset val="1"/>
     </font>
     <font>
-      <charset val="1"/>
-      <color theme="1"/>
-      <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color theme="1"/>
-      <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -136,7 +157,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -144,34 +165,61 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
+  <cellXfs count="5">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -351,19 +399,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:G335"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.6796875"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="15.14" customWidth="1"/>
-    <col min="2" max="2" width="30.43" customWidth="1"/>
-    <col min="3" max="3" width="13.71" customWidth="1"/>
-    <col min="4" max="4" width="19.71" customWidth="1"/>
-    <col min="5" max="6" width="10.71" customWidth="1"/>
-    <col min="7" max="7" width="30.71" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="30.71"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -386,188 +437,303 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E5" t="s">
-        <v>21</v>
+      <c r="E5" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="0" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E6" t="s">
-        <v>22</v>
+      <c r="E6" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="B7" t="s">
+      <c r="G8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="326" ht="15" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E326" s="3"/>
-      <c r="F326" s="3"/>
-    </row>
-    <row r="327" ht="15" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E327" s="3"/>
-      <c r="F327" s="3"/>
-    </row>
-    <row r="328" ht="15" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E328" s="3"/>
-      <c r="F328" s="3"/>
-    </row>
-    <row r="329" ht="15" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E329" s="3"/>
-      <c r="F329" s="3"/>
-    </row>
-    <row r="330" ht="15" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E330" s="3"/>
-      <c r="F330" s="3"/>
-    </row>
-    <row r="331" ht="15" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E331" s="3"/>
-      <c r="F331" s="3"/>
-    </row>
-    <row r="332" ht="15" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E332" s="3"/>
-      <c r="F332" s="3"/>
-    </row>
-    <row r="333" ht="15" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E333" s="3"/>
-      <c r="F333" s="3"/>
-    </row>
-    <row r="334" ht="15" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E334" s="3"/>
-      <c r="F334" s="3"/>
-    </row>
-    <row r="335" ht="15" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E335" s="3"/>
-      <c r="F335" s="3"/>
+      <c r="B10" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E326" s="4"/>
+      <c r="F326" s="4"/>
+    </row>
+    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E327" s="4"/>
+      <c r="F327" s="4"/>
+    </row>
+    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E328" s="4"/>
+      <c r="F328" s="4"/>
+    </row>
+    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E329" s="4"/>
+      <c r="F329" s="4"/>
+    </row>
+    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E330" s="4"/>
+      <c r="F330" s="4"/>
+    </row>
+    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E331" s="4"/>
+      <c r="F331" s="4"/>
+    </row>
+    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E332" s="4"/>
+      <c r="F332" s="4"/>
+    </row>
+    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E333" s="4"/>
+      <c r="F333" s="4"/>
+    </row>
+    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E334" s="4"/>
+      <c r="F334" s="4"/>
+    </row>
+    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E335" s="4"/>
+      <c r="F335" s="4"/>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.6796875"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.6796875"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/samples/sample_1/SAFE_VESSELS_INVENTORY_20251201.XLSX
+++ b/samples/sample_1/SAFE_VESSELS_INVENTORY_20251201.XLSX
@@ -54,7 +54,7 @@
     <t xml:space="preserve">cust 001</t>
   </si>
   <si>
-    <t xml:space="preserve">item 1</t>
+    <t xml:space="preserve">ITEM 1</t>
   </si>
   <si>
     <t xml:space="preserve">2026</t>
@@ -63,7 +63,7 @@
     <t xml:space="preserve">chart</t>
   </si>
   <si>
-    <t xml:space="preserve">item 2</t>
+    <t xml:space="preserve">ITEM 2</t>
   </si>
   <si>
     <t xml:space="preserve">2025 (3)</t>
@@ -72,7 +72,7 @@
     <t xml:space="preserve">book</t>
   </si>
   <si>
-    <t xml:space="preserve">item 3</t>
+    <t xml:space="preserve">ITEM 3</t>
   </si>
   <si>
     <t xml:space="preserve">1.2.0</t>
@@ -93,7 +93,7 @@
     <t xml:space="preserve">1.1.0</t>
   </si>
   <si>
-    <t xml:space="preserve">item 4</t>
+    <t xml:space="preserve">ITEM 4</t>
   </si>
   <si>
     <t xml:space="preserve">compass</t>
@@ -195,19 +195,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -406,248 +406,247 @@
   <dimension ref="A1:G335"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="30.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="30.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="0" t="s">
+      <c r="C8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="3" t="s">
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="0" t="s">
+      <c r="C12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="2" t="s">
         <v>24</v>
       </c>
     </row>

--- a/samples/sample_1/SAFE_VESSELS_INVENTORY_20251201.XLSX
+++ b/samples/sample_1/SAFE_VESSELS_INVENTORY_20251201.XLSX
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="29">
   <si>
     <t xml:space="preserve">SHIPID</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t xml:space="preserve">falcon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cust 002</t>
   </si>
   <si>
     <t xml:space="preserve">2025 (1)</t>
@@ -581,7 +584,7 @@
         <v>26</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>10</v>
@@ -601,13 +604,13 @@
         <v>26</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -621,7 +624,7 @@
         <v>26</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>16</v>
@@ -640,8 +643,8 @@
       <c r="B12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>9</v>
+      <c r="C12" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>23</v>
